--- a/tests/ui_tests/test_report.xlsx
+++ b/tests/ui_tests/test_report.xlsx
@@ -452,7 +452,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-02 21:23:58</t>
+          <t>2026-04-12 16:44:00</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-02 21:24:01</t>
+          <t>2026-04-12 16:44:03</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-02 21:24:05</t>
+          <t>2026-04-12 16:44:07</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-02 21:24:09</t>
+          <t>2026-04-12 16:44:11</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02 21:24:13</t>
+          <t>2026-04-12 16:44:14</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-02 21:24:17</t>
+          <t>2026-04-12 16:44:18</t>
         </is>
       </c>
     </row>
